--- a/config/achievement/achievement.xlsx
+++ b/config/achievement/achievement.xlsx
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>成長</t>
+          <t>人物成长</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>仲間収集</t>
+          <t>伙伴收集</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>仲間育成</t>
+          <t>伙伴培养</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ステージ</t>
+          <t>关卡</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>アリーナ</t>
+          <t>竞技场</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>好友</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
